--- a/Output/AllModels_SensitivityNoPushing_12000.xlsx
+++ b/Output/AllModels_SensitivityNoPushing_12000.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="218" uniqueCount="218">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="219" uniqueCount="219">
   <si>
     <t xml:space="preserve"/>
   </si>
@@ -89,7 +89,7 @@
     <t xml:space="preserve">3.65***</t>
   </si>
   <si>
-    <t xml:space="preserve">[ 3.45, 3.85]</t>
+    <t xml:space="preserve">[ 3.45, 3.86]</t>
   </si>
   <si>
     <t xml:space="preserve">0.31***</t>
@@ -215,7 +215,7 @@
     <t xml:space="preserve">[ 0.92,   1.04]</t>
   </si>
   <si>
-    <t xml:space="preserve">[-0.10, 0.11]</t>
+    <t xml:space="preserve">[-0.09, 0.11]</t>
   </si>
   <si>
     <t xml:space="preserve">1.32</t>
@@ -284,7 +284,7 @@
     <t xml:space="preserve">[ 1.02,   1.12]</t>
   </si>
   <si>
-    <t xml:space="preserve">0.09*</t>
+    <t xml:space="preserve">0.09**</t>
   </si>
   <si>
     <t xml:space="preserve">[ 0.02, 0.16]</t>
@@ -359,7 +359,7 @@
     <t xml:space="preserve">[ 0.85,   1.56]</t>
   </si>
   <si>
-    <t xml:space="preserve">0.44</t>
+    <t xml:space="preserve">0.43</t>
   </si>
   <si>
     <t xml:space="preserve">[-0.21, 1.08]</t>
@@ -395,7 +395,7 @@
     <t xml:space="preserve">0.36</t>
   </si>
   <si>
-    <t xml:space="preserve">[-0.27, 1.01]</t>
+    <t xml:space="preserve">[-0.29, 1.01]</t>
   </si>
   <si>
     <t xml:space="preserve">[0.21,   6.14]</t>
@@ -446,10 +446,10 @@
     <t xml:space="preserve">[ 0.68,   1.56]</t>
   </si>
   <si>
-    <t xml:space="preserve">-0.31</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[-1.19, 0.57]</t>
+    <t xml:space="preserve">-0.30</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[-1.20, 0.59]</t>
   </si>
   <si>
     <t xml:space="preserve">0.92</t>
@@ -491,136 +491,139 @@
     <t xml:space="preserve">[0.07, 0.32]</t>
   </si>
   <si>
+    <t xml:space="preserve">0.39</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[0.07, 0.64]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.99</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[0.17, 1.73]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">L3:sd(Daily individual's experienced persuasion)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[0.06, 0.44]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.13</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[0.09, 0.18]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.05</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[0.02, 0.08]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.07</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[0.01, 0.12]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.17</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[0.01, 0.48]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">L3:sd(Daily partner's experienced persuasion)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.15</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[0.01, 0.35]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[0.04, 0.12]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.06</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[0.03, 0.09]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.09</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[0.04, 0.14]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.50</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[0.16, 0.97]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">L3:sd(Daily individual's experienced pressure)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[0.01, 0.75]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[0.00, 0.25]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[0.00, 0.16]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.08</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[0.00, 0.26]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.82</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[0.05, 2.29]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">L3:sd(Daily partner's experienced pressure)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.35</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[0.02, 1.20]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[0.00, 0.20]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[0.00, 0.11]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[0.00, 0.24]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.87</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[0.05, 2.98]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">L3:sd(Daily individual's experienced pushing)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">L3:sd(Daily partner's experienced pushing)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Random Effects (Level 2 - Couple:Person)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">L2:sd(Intercept)</t>
+  </si>
+  <si>
     <t xml:space="preserve">0.38</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[0.06, 0.63]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.99</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[0.17, 1.73]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">L3:sd(Daily individual's experienced persuasion)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[0.06, 0.44]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.13</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[0.09, 0.18]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.05</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[0.02, 0.08]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.07</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[0.01, 0.12]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.17</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[0.01, 0.48]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">L3:sd(Daily partner's experienced persuasion)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.15</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[0.01, 0.35]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[0.04, 0.12]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.06</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[0.03, 0.09]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.09</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[0.04, 0.14]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.50</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[0.16, 0.97]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">L3:sd(Daily individual's experienced pressure)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[0.01, 0.75]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[0.00, 0.25]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[0.00, 0.16]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.08</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[0.00, 0.26]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.82</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[0.05, 2.29]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">L3:sd(Daily partner's experienced pressure)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.35</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[0.02, 1.20]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[0.00, 0.20]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[0.00, 0.11]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[0.00, 0.24]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.87</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[0.05, 2.98]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">L3:sd(Daily individual's experienced pushing)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">L3:sd(Daily partner's experienced pushing)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Random Effects (Level 2 - Couple:Person)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">L2:sd(Intercept)</t>
   </si>
   <si>
     <t xml:space="preserve">[0.18, 0.59]</t>
@@ -2014,94 +2017,94 @@
         <v>202</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>159</v>
+        <v>203</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="D33" s="1" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="E33" s="1" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="F33" s="1" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="G33" s="1" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="H33" s="1" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="I33" s="1" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="J33" s="1" t="s">
         <v>32</v>
       </c>
       <c r="K33" s="1" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="6" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="C34" s="1" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="E34" s="1" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="F34" s="1" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="G34" s="1" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="H34" s="1" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="I34" s="1" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="J34" s="1" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="K34" s="1" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="8" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="B35" s="4"/>
       <c r="C35" s="4"/>
       <c r="D35" s="4" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="E35" s="4" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="F35" s="4" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="G35" s="4" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="H35" s="4" t="s">
         <v>197</v>
       </c>
       <c r="I35" s="4" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="J35" s="4"/>
       <c r="K35" s="4"/>

--- a/Output/AllModels_SensitivityNoPushing_12000.xlsx
+++ b/Output/AllModels_SensitivityNoPushing_12000.xlsx
@@ -1,682 +1,689 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <workbookPr date1904="false"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29029"/>
+  <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kueng\DataAnalysis\02TimeAndTiesControl\Output\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9EBCD4D5-F2D5-417C-BB3B-CEB718F6B4AD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="13125" windowHeight="6105" firstSheet="0" activeTab="0"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="219" uniqueCount="219">
-  <si>
-    <t xml:space="preserve"/>
-  </si>
-  <si>
-    <t xml:space="preserve">Subjective MVPA Hurdle Lognormal</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Device-Based MVPA Log (Gaussian)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mood Gaussian</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reactance Dichotome</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hurdle</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Non-Zero</t>
-  </si>
-  <si>
-    <t xml:space="preserve">exp(Est.)_hu pa_sub</t>
-  </si>
-  <si>
-    <t xml:space="preserve">95% CI_hu pa_sub</t>
-  </si>
-  <si>
-    <t xml:space="preserve">exp(Est.)_nonzero pa_sub</t>
-  </si>
-  <si>
-    <t xml:space="preserve">95% CI_nonzero pa_sub</t>
-  </si>
-  <si>
-    <t xml:space="preserve">exp(Est.) pa_obj_log</t>
-  </si>
-  <si>
-    <t xml:space="preserve">95% CI pa_obj_log</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Est. mood_gauss</t>
-  </si>
-  <si>
-    <t xml:space="preserve">95% CI mood_gauss</t>
-  </si>
-  <si>
-    <t xml:space="preserve">OR is_reactance</t>
-  </si>
-  <si>
-    <t xml:space="preserve">95% CI is_reactance</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Intercept</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.21***</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[ 0.15,  0.29]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">37.25***</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[31.84, 43.54]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">109.71***</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[98.95, 121.64]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.65***</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[ 3.45, 3.86]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.31***</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[0.16,   0.60]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Within-Person Effects</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Daily individual's experienced persuasion</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.55***</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[ 1.36,  1.82]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.03</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[ 0.97,  1.09]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[ 1.00,   1.06]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[-0.03, 0.05]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.86</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[0.71,   1.03]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Daily partner's experienced persuasion</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.37***</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[ 1.22,  1.56]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.02</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[ 0.98,  1.07]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[ 0.99,   1.05]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.03</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[-0.01, 0.08]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.13</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[0.85,   1.57]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Daily individual's experienced pressure</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[ 0.75,  1.40]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.89*</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[ 0.79,  0.98]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.96</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[ 0.89,   1.02]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-0.03</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[-0.14, 0.07]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.17*</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[1.23,   4.94]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Daily partner's experienced pressure</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68**</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[ 1.15,  2.90]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.94</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[ 0.85,  1.02]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.98</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[ 0.92,   1.04]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[-0.09, 0.11]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.32</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[0.54,   4.50]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Daily individual's experienced pushing</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Daily partner's experienced pushing</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Day</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.79</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[ 0.59,  1.06]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.95</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[ 0.84,  1.06]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.97</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[ 0.91,   1.04]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.25***</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[ 0.15, 0.35]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[0.83,   3.95]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Own action plan</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.38***</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[ 8.49, 12.76]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.35***</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[ 1.23,  1.48]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.07**</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[ 1.02,   1.12]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.09**</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[ 0.02, 0.16]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.14</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[0.62,   2.11]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Partner action plan</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.26*</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[ 1.03,  1.54]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.07</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[ 0.99,  1.16]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.05*</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[ 1.01,   1.10]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.02</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[-0.05, 0.09]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.83</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[0.46,   1.47]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Daily wear time</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.00***</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[ 1.00,   1.00]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Between-Person Effects</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mean individual's experienced persuasion</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[ 0.80,  3.51]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[ 0.82,  1.59]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.15</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[ 0.85,   1.56]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.43</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[-0.21, 1.08]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[0.38,   9.47]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mean partner's experienced persuasion</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.72</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[ 0.82,  3.63]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[ 0.72,  1.38]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.05</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[ 0.76,   1.44]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.36</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[-0.29, 1.01]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[0.21,   6.14]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mean individual's experienced pressure</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.16***</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[ 0.05,  0.45]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[ 0.48,  1.93]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[ 0.56,   1.34]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-0.37</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[-1.26, 0.51]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.05**</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[2.82, 584.24]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mean partner's experienced pressure</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.32*</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[ 0.10,  0.91]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.88</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[ 0.44,  1.76]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[ 0.68,   1.56]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-0.30</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[-1.20, 0.59]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.92</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[0.05,  13.14]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mean individual's experienced pushing</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mean partner's experienced pushing</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mean wear time</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Random Effects (Level 3 - Couple)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">L3:sd(Intercept)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.75</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[0.53, 1.04]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.25</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[0.14, 0.37]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.20</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[0.07, 0.32]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.39</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[0.07, 0.64]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.99</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[0.17, 1.73]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">L3:sd(Daily individual's experienced persuasion)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[0.06, 0.44]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.13</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[0.09, 0.18]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.05</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[0.02, 0.08]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.07</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[0.01, 0.12]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.17</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[0.01, 0.48]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">L3:sd(Daily partner's experienced persuasion)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.15</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[0.01, 0.35]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[0.04, 0.12]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.06</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[0.03, 0.09]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.09</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[0.04, 0.14]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.50</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[0.16, 0.97]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">L3:sd(Daily individual's experienced pressure)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[0.01, 0.75]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[0.00, 0.25]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[0.00, 0.16]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.08</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[0.00, 0.26]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.82</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[0.05, 2.29]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">L3:sd(Daily partner's experienced pressure)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.35</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[0.02, 1.20]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[0.00, 0.20]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[0.00, 0.11]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[0.00, 0.24]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.87</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[0.05, 2.98]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">L3:sd(Daily individual's experienced pushing)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">L3:sd(Daily partner's experienced pushing)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Random Effects (Level 2 - Couple:Person)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">L2:sd(Intercept)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.38</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[0.18, 0.59]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.23</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[0.16, 0.33]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.27</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[0.21, 0.35]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.61</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[0.48, 0.78]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[0.44, 1.68]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Additional Parameters</t>
-  </si>
-  <si>
-    <t xml:space="preserve">sigma</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.66</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[0.64, 0.69]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.55</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[0.53, 0.56]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[0.85, 0.89]</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="305" uniqueCount="219">
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>Subjective MVPA Hurdle Lognormal</t>
+  </si>
+  <si>
+    <t>Device-Based MVPA Log (Gaussian)</t>
+  </si>
+  <si>
+    <t>Mood Gaussian</t>
+  </si>
+  <si>
+    <t>Reactance Dichotome</t>
+  </si>
+  <si>
+    <t>Hurdle</t>
+  </si>
+  <si>
+    <t>Non-Zero</t>
+  </si>
+  <si>
+    <t>exp(Est.)_hu pa_sub</t>
+  </si>
+  <si>
+    <t>95% CI_hu pa_sub</t>
+  </si>
+  <si>
+    <t>exp(Est.)_nonzero pa_sub</t>
+  </si>
+  <si>
+    <t>95% CI_nonzero pa_sub</t>
+  </si>
+  <si>
+    <t>exp(Est.) pa_obj_log</t>
+  </si>
+  <si>
+    <t>95% CI pa_obj_log</t>
+  </si>
+  <si>
+    <t>Est. mood_gauss</t>
+  </si>
+  <si>
+    <t>95% CI mood_gauss</t>
+  </si>
+  <si>
+    <t>OR is_reactance</t>
+  </si>
+  <si>
+    <t>95% CI is_reactance</t>
+  </si>
+  <si>
+    <t>Intercept</t>
+  </si>
+  <si>
+    <t>0.21***</t>
+  </si>
+  <si>
+    <t>[ 0.15,  0.29]</t>
+  </si>
+  <si>
+    <t>37.25***</t>
+  </si>
+  <si>
+    <t>[31.84, 43.54]</t>
+  </si>
+  <si>
+    <t>109.71***</t>
+  </si>
+  <si>
+    <t>[98.95, 121.64]</t>
+  </si>
+  <si>
+    <t>3.65***</t>
+  </si>
+  <si>
+    <t>[ 3.45, 3.86]</t>
+  </si>
+  <si>
+    <t>0.31***</t>
+  </si>
+  <si>
+    <t>[0.16,   0.60]</t>
+  </si>
+  <si>
+    <t>Within-Person Effects</t>
+  </si>
+  <si>
+    <t>Daily individual's experienced persuasion</t>
+  </si>
+  <si>
+    <t>1.55***</t>
+  </si>
+  <si>
+    <t>[ 1.36,  1.82]</t>
+  </si>
+  <si>
+    <t>1.03</t>
+  </si>
+  <si>
+    <t>[ 0.97,  1.09]</t>
+  </si>
+  <si>
+    <t>[ 1.00,   1.06]</t>
+  </si>
+  <si>
+    <t>0.01</t>
+  </si>
+  <si>
+    <t>[-0.03, 0.05]</t>
+  </si>
+  <si>
+    <t>0.86</t>
+  </si>
+  <si>
+    <t>[0.71,   1.03]</t>
+  </si>
+  <si>
+    <t>Daily partner's experienced persuasion</t>
+  </si>
+  <si>
+    <t>1.37***</t>
+  </si>
+  <si>
+    <t>[ 1.22,  1.56]</t>
+  </si>
+  <si>
+    <t>1.02</t>
+  </si>
+  <si>
+    <t>[ 0.98,  1.07]</t>
+  </si>
+  <si>
+    <t>[ 0.99,   1.05]</t>
+  </si>
+  <si>
+    <t>0.03</t>
+  </si>
+  <si>
+    <t>[-0.01, 0.08]</t>
+  </si>
+  <si>
+    <t>1.13</t>
+  </si>
+  <si>
+    <t>[0.85,   1.57]</t>
+  </si>
+  <si>
+    <t>Daily individual's experienced pressure</t>
+  </si>
+  <si>
+    <t>1.01</t>
+  </si>
+  <si>
+    <t>[ 0.75,  1.40]</t>
+  </si>
+  <si>
+    <t>0.89*</t>
+  </si>
+  <si>
+    <t>[ 0.79,  0.98]</t>
+  </si>
+  <si>
+    <t>0.96</t>
+  </si>
+  <si>
+    <t>[ 0.89,   1.02]</t>
+  </si>
+  <si>
+    <t>-0.03</t>
+  </si>
+  <si>
+    <t>[-0.14, 0.07]</t>
+  </si>
+  <si>
+    <t>2.17*</t>
+  </si>
+  <si>
+    <t>[1.23,   4.94]</t>
+  </si>
+  <si>
+    <t>Daily partner's experienced pressure</t>
+  </si>
+  <si>
+    <t>1.68**</t>
+  </si>
+  <si>
+    <t>[ 1.15,  2.90]</t>
+  </si>
+  <si>
+    <t>0.94</t>
+  </si>
+  <si>
+    <t>[ 0.85,  1.02]</t>
+  </si>
+  <si>
+    <t>0.98</t>
+  </si>
+  <si>
+    <t>[ 0.92,   1.04]</t>
+  </si>
+  <si>
+    <t>[-0.09, 0.11]</t>
+  </si>
+  <si>
+    <t>1.32</t>
+  </si>
+  <si>
+    <t>[0.54,   4.50]</t>
+  </si>
+  <si>
+    <t>Daily individual's experienced pushing</t>
+  </si>
+  <si>
+    <t>Daily partner's experienced pushing</t>
+  </si>
+  <si>
+    <t>Day</t>
+  </si>
+  <si>
+    <t>0.79</t>
+  </si>
+  <si>
+    <t>[ 0.59,  1.06]</t>
+  </si>
+  <si>
+    <t>0.95</t>
+  </si>
+  <si>
+    <t>[ 0.84,  1.06]</t>
+  </si>
+  <si>
+    <t>0.97</t>
+  </si>
+  <si>
+    <t>[ 0.91,   1.04]</t>
+  </si>
+  <si>
+    <t>0.25***</t>
+  </si>
+  <si>
+    <t>[ 0.15, 0.35]</t>
+  </si>
+  <si>
+    <t>1.80</t>
+  </si>
+  <si>
+    <t>[0.83,   3.95]</t>
+  </si>
+  <si>
+    <t>Own action plan</t>
+  </si>
+  <si>
+    <t>10.38***</t>
+  </si>
+  <si>
+    <t>[ 8.49, 12.76]</t>
+  </si>
+  <si>
+    <t>1.35***</t>
+  </si>
+  <si>
+    <t>[ 1.23,  1.48]</t>
+  </si>
+  <si>
+    <t>1.07**</t>
+  </si>
+  <si>
+    <t>[ 1.02,   1.12]</t>
+  </si>
+  <si>
+    <t>0.09**</t>
+  </si>
+  <si>
+    <t>[ 0.02, 0.16]</t>
+  </si>
+  <si>
+    <t>1.14</t>
+  </si>
+  <si>
+    <t>[0.62,   2.11]</t>
+  </si>
+  <si>
+    <t>Partner action plan</t>
+  </si>
+  <si>
+    <t>1.26*</t>
+  </si>
+  <si>
+    <t>[ 1.03,  1.54]</t>
+  </si>
+  <si>
+    <t>1.07</t>
+  </si>
+  <si>
+    <t>[ 0.99,  1.16]</t>
+  </si>
+  <si>
+    <t>1.05*</t>
+  </si>
+  <si>
+    <t>[ 1.01,   1.10]</t>
+  </si>
+  <si>
+    <t>0.02</t>
+  </si>
+  <si>
+    <t>[-0.05, 0.09]</t>
+  </si>
+  <si>
+    <t>0.83</t>
+  </si>
+  <si>
+    <t>[0.46,   1.47]</t>
+  </si>
+  <si>
+    <t>Daily wear time</t>
+  </si>
+  <si>
+    <t>1.00***</t>
+  </si>
+  <si>
+    <t>[ 1.00,   1.00]</t>
+  </si>
+  <si>
+    <t>Between-Person Effects</t>
+  </si>
+  <si>
+    <t>Mean individual's experienced persuasion</t>
+  </si>
+  <si>
+    <t>1.68</t>
+  </si>
+  <si>
+    <t>[ 0.80,  3.51]</t>
+  </si>
+  <si>
+    <t>[ 0.82,  1.59]</t>
+  </si>
+  <si>
+    <t>1.15</t>
+  </si>
+  <si>
+    <t>[ 0.85,   1.56]</t>
+  </si>
+  <si>
+    <t>0.43</t>
+  </si>
+  <si>
+    <t>[-0.21, 1.08]</t>
+  </si>
+  <si>
+    <t>1.81</t>
+  </si>
+  <si>
+    <t>[0.38,   9.47]</t>
+  </si>
+  <si>
+    <t>Mean partner's experienced persuasion</t>
+  </si>
+  <si>
+    <t>1.72</t>
+  </si>
+  <si>
+    <t>[ 0.82,  3.63]</t>
+  </si>
+  <si>
+    <t>1.00</t>
+  </si>
+  <si>
+    <t>[ 0.72,  1.38]</t>
+  </si>
+  <si>
+    <t>1.05</t>
+  </si>
+  <si>
+    <t>[ 0.76,   1.44]</t>
+  </si>
+  <si>
+    <t>0.36</t>
+  </si>
+  <si>
+    <t>[-0.29, 1.01]</t>
+  </si>
+  <si>
+    <t>[0.21,   6.14]</t>
+  </si>
+  <si>
+    <t>Mean individual's experienced pressure</t>
+  </si>
+  <si>
+    <t>0.16***</t>
+  </si>
+  <si>
+    <t>[ 0.05,  0.45]</t>
+  </si>
+  <si>
+    <t>[ 0.48,  1.93]</t>
+  </si>
+  <si>
+    <t>[ 0.56,   1.34]</t>
+  </si>
+  <si>
+    <t>-0.37</t>
+  </si>
+  <si>
+    <t>[-1.26, 0.51]</t>
+  </si>
+  <si>
+    <t>33.05**</t>
+  </si>
+  <si>
+    <t>[2.82, 584.24]</t>
+  </si>
+  <si>
+    <t>Mean partner's experienced pressure</t>
+  </si>
+  <si>
+    <t>0.32*</t>
+  </si>
+  <si>
+    <t>[ 0.10,  0.91]</t>
+  </si>
+  <si>
+    <t>0.88</t>
+  </si>
+  <si>
+    <t>[ 0.44,  1.76]</t>
+  </si>
+  <si>
+    <t>[ 0.68,   1.56]</t>
+  </si>
+  <si>
+    <t>-0.30</t>
+  </si>
+  <si>
+    <t>[-1.20, 0.59]</t>
+  </si>
+  <si>
+    <t>0.92</t>
+  </si>
+  <si>
+    <t>[0.05,  13.14]</t>
+  </si>
+  <si>
+    <t>Mean individual's experienced pushing</t>
+  </si>
+  <si>
+    <t>Mean partner's experienced pushing</t>
+  </si>
+  <si>
+    <t>Mean wear time</t>
+  </si>
+  <si>
+    <t>Random Effects (Level 3 - Couple)</t>
+  </si>
+  <si>
+    <t>L3:sd(Intercept)</t>
+  </si>
+  <si>
+    <t>0.75</t>
+  </si>
+  <si>
+    <t>[0.53, 1.04]</t>
+  </si>
+  <si>
+    <t>0.25</t>
+  </si>
+  <si>
+    <t>[0.14, 0.37]</t>
+  </si>
+  <si>
+    <t>0.20</t>
+  </si>
+  <si>
+    <t>[0.07, 0.32]</t>
+  </si>
+  <si>
+    <t>0.39</t>
+  </si>
+  <si>
+    <t>[0.07, 0.64]</t>
+  </si>
+  <si>
+    <t>0.99</t>
+  </si>
+  <si>
+    <t>[0.17, 1.73]</t>
+  </si>
+  <si>
+    <t>L3:sd(Daily individual's experienced persuasion)</t>
+  </si>
+  <si>
+    <t>[0.06, 0.44]</t>
+  </si>
+  <si>
+    <t>0.13</t>
+  </si>
+  <si>
+    <t>[0.09, 0.18]</t>
+  </si>
+  <si>
+    <t>0.05</t>
+  </si>
+  <si>
+    <t>[0.02, 0.08]</t>
+  </si>
+  <si>
+    <t>0.07</t>
+  </si>
+  <si>
+    <t>[0.01, 0.12]</t>
+  </si>
+  <si>
+    <t>0.17</t>
+  </si>
+  <si>
+    <t>[0.01, 0.48]</t>
+  </si>
+  <si>
+    <t>L3:sd(Daily partner's experienced persuasion)</t>
+  </si>
+  <si>
+    <t>0.15</t>
+  </si>
+  <si>
+    <t>[0.01, 0.35]</t>
+  </si>
+  <si>
+    <t>[0.04, 0.12]</t>
+  </si>
+  <si>
+    <t>0.06</t>
+  </si>
+  <si>
+    <t>[0.03, 0.09]</t>
+  </si>
+  <si>
+    <t>0.09</t>
+  </si>
+  <si>
+    <t>[0.04, 0.14]</t>
+  </si>
+  <si>
+    <t>0.50</t>
+  </si>
+  <si>
+    <t>[0.16, 0.97]</t>
+  </si>
+  <si>
+    <t>L3:sd(Daily individual's experienced pressure)</t>
+  </si>
+  <si>
+    <t>[0.01, 0.75]</t>
+  </si>
+  <si>
+    <t>[0.00, 0.25]</t>
+  </si>
+  <si>
+    <t>[0.00, 0.16]</t>
+  </si>
+  <si>
+    <t>0.08</t>
+  </si>
+  <si>
+    <t>[0.00, 0.26]</t>
+  </si>
+  <si>
+    <t>0.82</t>
+  </si>
+  <si>
+    <t>[0.05, 2.29]</t>
+  </si>
+  <si>
+    <t>L3:sd(Daily partner's experienced pressure)</t>
+  </si>
+  <si>
+    <t>0.35</t>
+  </si>
+  <si>
+    <t>[0.02, 1.20]</t>
+  </si>
+  <si>
+    <t>[0.00, 0.20]</t>
+  </si>
+  <si>
+    <t>[0.00, 0.11]</t>
+  </si>
+  <si>
+    <t>[0.00, 0.24]</t>
+  </si>
+  <si>
+    <t>0.87</t>
+  </si>
+  <si>
+    <t>[0.05, 2.98]</t>
+  </si>
+  <si>
+    <t>L3:sd(Daily individual's experienced pushing)</t>
+  </si>
+  <si>
+    <t>L3:sd(Daily partner's experienced pushing)</t>
+  </si>
+  <si>
+    <t>Random Effects (Level 2 - Couple:Person)</t>
+  </si>
+  <si>
+    <t>L2:sd(Intercept)</t>
+  </si>
+  <si>
+    <t>0.38</t>
+  </si>
+  <si>
+    <t>[0.18, 0.59]</t>
+  </si>
+  <si>
+    <t>0.23</t>
+  </si>
+  <si>
+    <t>[0.16, 0.33]</t>
+  </si>
+  <si>
+    <t>0.27</t>
+  </si>
+  <si>
+    <t>[0.21, 0.35]</t>
+  </si>
+  <si>
+    <t>0.61</t>
+  </si>
+  <si>
+    <t>[0.48, 0.78]</t>
+  </si>
+  <si>
+    <t>[0.44, 1.68]</t>
+  </si>
+  <si>
+    <t>Additional Parameters</t>
+  </si>
+  <si>
+    <t>sigma</t>
+  </si>
+  <si>
+    <t>0.66</t>
+  </si>
+  <si>
+    <t>[0.64, 0.69]</t>
+  </si>
+  <si>
+    <t>0.55</t>
+  </si>
+  <si>
+    <t>[0.53, 0.56]</t>
+  </si>
+  <si>
+    <t>[0.85, 0.89]</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="0"/>
-  <fonts count="4">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
@@ -690,16 +697,16 @@
       <name val="Calibri"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
-      <b/>
     </font>
     <font>
+      <i/>
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
-      <i/>
     </font>
   </fonts>
   <fills count="2">
@@ -719,20 +726,28 @@
       <diagonal/>
     </border>
     <border>
+      <left/>
+      <right/>
       <top style="thin">
         <color rgb="FF000000"/>
       </top>
+      <bottom/>
+      <diagonal/>
     </border>
     <border>
+      <left/>
+      <right/>
+      <top/>
       <bottom style="thin">
         <color rgb="FF000000"/>
       </bottom>
+      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -745,20 +760,35 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment indent="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -1040,46 +1070,59 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:K41"/>
+  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="46" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="19.140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="16.85546875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="24.28515625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="22.140625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="19.28515625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="17" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="15.7109375" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="18.42578125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="15.140625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="18.42578125" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="5" t="s">
+      <c r="B1" s="8" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="5" t="s">
+      <c r="C1" s="8" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="5" t="s">
+      <c r="D1" s="8" t="s">
         <v>1</v>
       </c>
-      <c r="E1" s="5" t="s">
+      <c r="E1" s="8" t="s">
         <v>1</v>
       </c>
-      <c r="F1" s="5" t="s">
+      <c r="F1" s="8" t="s">
         <v>2</v>
       </c>
-      <c r="G1" s="5" t="s">
+      <c r="G1" s="8" t="s">
         <v>2</v>
       </c>
-      <c r="H1" s="5" t="s">
+      <c r="H1" s="8" t="s">
         <v>3</v>
       </c>
-      <c r="I1" s="5" t="s">
+      <c r="I1" s="8" t="s">
         <v>3</v>
       </c>
-      <c r="J1" s="5" t="s">
+      <c r="J1" s="8" t="s">
         <v>4</v>
       </c>
-      <c r="K1" s="5" t="s">
+      <c r="K1" s="8" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
         <v>0</v>
       </c>
@@ -1114,7 +1157,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
         <v>0</v>
       </c>
@@ -1149,7 +1192,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="4">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>17</v>
       </c>
@@ -1184,43 +1227,43 @@
         <v>27</v>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" s="6" t="s">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A5" s="9" t="s">
         <v>28</v>
       </c>
-      <c r="B5" s="1" t="s">
+      <c r="B5" s="10" t="s">
         <v>28</v>
       </c>
-      <c r="C5" s="1" t="s">
+      <c r="C5" s="10" t="s">
         <v>28</v>
       </c>
-      <c r="D5" s="1" t="s">
+      <c r="D5" s="10" t="s">
         <v>28</v>
       </c>
-      <c r="E5" s="1" t="s">
+      <c r="E5" s="10" t="s">
         <v>28</v>
       </c>
-      <c r="F5" s="1" t="s">
+      <c r="F5" s="10" t="s">
         <v>28</v>
       </c>
-      <c r="G5" s="1" t="s">
+      <c r="G5" s="10" t="s">
         <v>28</v>
       </c>
-      <c r="H5" s="1" t="s">
+      <c r="H5" s="10" t="s">
         <v>28</v>
       </c>
-      <c r="I5" s="1" t="s">
+      <c r="I5" s="10" t="s">
         <v>28</v>
       </c>
-      <c r="J5" s="1" t="s">
+      <c r="J5" s="10" t="s">
         <v>28</v>
       </c>
-      <c r="K5" s="1" t="s">
+      <c r="K5" s="10" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" s="7" t="s">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A6" s="6" t="s">
         <v>29</v>
       </c>
       <c r="B6" s="5" t="s">
@@ -1254,8 +1297,8 @@
         <v>38</v>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" s="7" t="s">
+    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A7" s="6" t="s">
         <v>39</v>
       </c>
       <c r="B7" s="5" t="s">
@@ -1289,8 +1332,8 @@
         <v>48</v>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" s="7" t="s">
+    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A8" s="6" t="s">
         <v>49</v>
       </c>
       <c r="B8" s="1" t="s">
@@ -1324,8 +1367,8 @@
         <v>59</v>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" s="7" t="s">
+    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A9" s="6" t="s">
         <v>60</v>
       </c>
       <c r="B9" s="5" t="s">
@@ -1359,8 +1402,8 @@
         <v>69</v>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" s="7" t="s">
+    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A10" s="6" t="s">
         <v>70</v>
       </c>
       <c r="B10" s="1"/>
@@ -1374,8 +1417,8 @@
       <c r="J10" s="1"/>
       <c r="K10" s="1"/>
     </row>
-    <row r="11">
-      <c r="A11" s="7" t="s">
+    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A11" s="6" t="s">
         <v>71</v>
       </c>
       <c r="B11" s="1"/>
@@ -1389,8 +1432,8 @@
       <c r="J11" s="1"/>
       <c r="K11" s="1"/>
     </row>
-    <row r="12">
-      <c r="A12" s="7" t="s">
+    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A12" s="6" t="s">
         <v>72</v>
       </c>
       <c r="B12" s="1" t="s">
@@ -1424,8 +1467,8 @@
         <v>82</v>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" s="7" t="s">
+    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A13" s="6" t="s">
         <v>83</v>
       </c>
       <c r="B13" s="5" t="s">
@@ -1459,8 +1502,8 @@
         <v>93</v>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" s="7" t="s">
+    <row r="14" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A14" s="6" t="s">
         <v>94</v>
       </c>
       <c r="B14" s="5" t="s">
@@ -1494,8 +1537,8 @@
         <v>104</v>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" s="7" t="s">
+    <row r="15" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A15" s="6" t="s">
         <v>105</v>
       </c>
       <c r="B15" s="1"/>
@@ -1513,43 +1556,43 @@
       <c r="J15" s="1"/>
       <c r="K15" s="1"/>
     </row>
-    <row r="16">
-      <c r="A16" s="6" t="s">
+    <row r="16" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A16" s="9" t="s">
         <v>108</v>
       </c>
-      <c r="B16" s="1" t="s">
+      <c r="B16" s="10" t="s">
         <v>108</v>
       </c>
-      <c r="C16" s="1" t="s">
+      <c r="C16" s="10" t="s">
         <v>108</v>
       </c>
-      <c r="D16" s="1" t="s">
+      <c r="D16" s="10" t="s">
         <v>108</v>
       </c>
-      <c r="E16" s="1" t="s">
+      <c r="E16" s="10" t="s">
         <v>108</v>
       </c>
-      <c r="F16" s="1" t="s">
+      <c r="F16" s="10" t="s">
         <v>108</v>
       </c>
-      <c r="G16" s="1" t="s">
+      <c r="G16" s="10" t="s">
         <v>108</v>
       </c>
-      <c r="H16" s="1" t="s">
+      <c r="H16" s="10" t="s">
         <v>108</v>
       </c>
-      <c r="I16" s="1" t="s">
+      <c r="I16" s="10" t="s">
         <v>108</v>
       </c>
-      <c r="J16" s="1" t="s">
+      <c r="J16" s="10" t="s">
         <v>108</v>
       </c>
-      <c r="K16" s="1" t="s">
+      <c r="K16" s="10" t="s">
         <v>108</v>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" s="7" t="s">
+    <row r="17" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A17" s="6" t="s">
         <v>109</v>
       </c>
       <c r="B17" s="1" t="s">
@@ -1583,8 +1626,8 @@
         <v>118</v>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" s="7" t="s">
+    <row r="18" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A18" s="6" t="s">
         <v>119</v>
       </c>
       <c r="B18" s="1" t="s">
@@ -1618,8 +1661,8 @@
         <v>128</v>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" s="7" t="s">
+    <row r="19" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A19" s="6" t="s">
         <v>129</v>
       </c>
       <c r="B19" s="5" t="s">
@@ -1653,8 +1696,8 @@
         <v>137</v>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" s="7" t="s">
+    <row r="20" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A20" s="6" t="s">
         <v>138</v>
       </c>
       <c r="B20" s="5" t="s">
@@ -1688,8 +1731,8 @@
         <v>147</v>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" s="7" t="s">
+    <row r="21" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A21" s="6" t="s">
         <v>148</v>
       </c>
       <c r="B21" s="1"/>
@@ -1703,8 +1746,8 @@
       <c r="J21" s="1"/>
       <c r="K21" s="1"/>
     </row>
-    <row r="22">
-      <c r="A22" s="7" t="s">
+    <row r="22" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A22" s="6" t="s">
         <v>149</v>
       </c>
       <c r="B22" s="1"/>
@@ -1718,8 +1761,8 @@
       <c r="J22" s="1"/>
       <c r="K22" s="1"/>
     </row>
-    <row r="23">
-      <c r="A23" s="7" t="s">
+    <row r="23" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A23" s="6" t="s">
         <v>150</v>
       </c>
       <c r="B23" s="1"/>
@@ -1737,43 +1780,43 @@
       <c r="J23" s="1"/>
       <c r="K23" s="1"/>
     </row>
-    <row r="24">
-      <c r="A24" s="6" t="s">
+    <row r="24" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A24" s="9" t="s">
         <v>151</v>
       </c>
-      <c r="B24" s="1" t="s">
+      <c r="B24" s="10" t="s">
         <v>151</v>
       </c>
-      <c r="C24" s="1" t="s">
+      <c r="C24" s="10" t="s">
         <v>151</v>
       </c>
-      <c r="D24" s="1" t="s">
+      <c r="D24" s="10" t="s">
         <v>151</v>
       </c>
-      <c r="E24" s="1" t="s">
+      <c r="E24" s="10" t="s">
         <v>151</v>
       </c>
-      <c r="F24" s="1" t="s">
+      <c r="F24" s="10" t="s">
         <v>151</v>
       </c>
-      <c r="G24" s="1" t="s">
+      <c r="G24" s="10" t="s">
         <v>151</v>
       </c>
-      <c r="H24" s="1" t="s">
+      <c r="H24" s="10" t="s">
         <v>151</v>
       </c>
-      <c r="I24" s="1" t="s">
+      <c r="I24" s="10" t="s">
         <v>151</v>
       </c>
-      <c r="J24" s="1" t="s">
+      <c r="J24" s="10" t="s">
         <v>151</v>
       </c>
-      <c r="K24" s="1" t="s">
+      <c r="K24" s="10" t="s">
         <v>151</v>
       </c>
     </row>
-    <row r="25">
-      <c r="A25" s="7" t="s">
+    <row r="25" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A25" s="6" t="s">
         <v>152</v>
       </c>
       <c r="B25" s="1" t="s">
@@ -1807,8 +1850,8 @@
         <v>162</v>
       </c>
     </row>
-    <row r="26">
-      <c r="A26" s="7" t="s">
+    <row r="26" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A26" s="6" t="s">
         <v>163</v>
       </c>
       <c r="B26" s="1" t="s">
@@ -1842,8 +1885,8 @@
         <v>172</v>
       </c>
     </row>
-    <row r="27">
-      <c r="A27" s="7" t="s">
+    <row r="27" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A27" s="6" t="s">
         <v>173</v>
       </c>
       <c r="B27" s="1" t="s">
@@ -1877,8 +1920,8 @@
         <v>182</v>
       </c>
     </row>
-    <row r="28">
-      <c r="A28" s="7" t="s">
+    <row r="28" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A28" s="6" t="s">
         <v>183</v>
       </c>
       <c r="B28" s="1" t="s">
@@ -1912,8 +1955,8 @@
         <v>190</v>
       </c>
     </row>
-    <row r="29">
-      <c r="A29" s="7" t="s">
+    <row r="29" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A29" s="6" t="s">
         <v>191</v>
       </c>
       <c r="B29" s="1" t="s">
@@ -1947,8 +1990,8 @@
         <v>198</v>
       </c>
     </row>
-    <row r="30">
-      <c r="A30" s="7" t="s">
+    <row r="30" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A30" s="6" t="s">
         <v>199</v>
       </c>
       <c r="B30" s="1"/>
@@ -1962,8 +2005,8 @@
       <c r="J30" s="1"/>
       <c r="K30" s="1"/>
     </row>
-    <row r="31">
-      <c r="A31" s="7" t="s">
+    <row r="31" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A31" s="6" t="s">
         <v>200</v>
       </c>
       <c r="B31" s="1"/>
@@ -1977,43 +2020,43 @@
       <c r="J31" s="1"/>
       <c r="K31" s="1"/>
     </row>
-    <row r="32">
-      <c r="A32" s="6" t="s">
+    <row r="32" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A32" s="9" t="s">
         <v>201</v>
       </c>
-      <c r="B32" s="1" t="s">
+      <c r="B32" s="10" t="s">
         <v>201</v>
       </c>
-      <c r="C32" s="1" t="s">
+      <c r="C32" s="10" t="s">
         <v>201</v>
       </c>
-      <c r="D32" s="1" t="s">
+      <c r="D32" s="10" t="s">
         <v>201</v>
       </c>
-      <c r="E32" s="1" t="s">
+      <c r="E32" s="10" t="s">
         <v>201</v>
       </c>
-      <c r="F32" s="1" t="s">
+      <c r="F32" s="10" t="s">
         <v>201</v>
       </c>
-      <c r="G32" s="1" t="s">
+      <c r="G32" s="10" t="s">
         <v>201</v>
       </c>
-      <c r="H32" s="1" t="s">
+      <c r="H32" s="10" t="s">
         <v>201</v>
       </c>
-      <c r="I32" s="1" t="s">
+      <c r="I32" s="10" t="s">
         <v>201</v>
       </c>
-      <c r="J32" s="1" t="s">
+      <c r="J32" s="10" t="s">
         <v>201</v>
       </c>
-      <c r="K32" s="1" t="s">
+      <c r="K32" s="10" t="s">
         <v>201</v>
       </c>
     </row>
-    <row r="33">
-      <c r="A33" s="7" t="s">
+    <row r="33" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A33" s="6" t="s">
         <v>202</v>
       </c>
       <c r="B33" s="1" t="s">
@@ -2047,43 +2090,43 @@
         <v>211</v>
       </c>
     </row>
-    <row r="34">
-      <c r="A34" s="6" t="s">
+    <row r="34" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A34" s="9" t="s">
         <v>212</v>
       </c>
-      <c r="B34" s="1" t="s">
+      <c r="B34" s="10" t="s">
         <v>212</v>
       </c>
-      <c r="C34" s="1" t="s">
+      <c r="C34" s="10" t="s">
         <v>212</v>
       </c>
-      <c r="D34" s="1" t="s">
+      <c r="D34" s="10" t="s">
         <v>212</v>
       </c>
-      <c r="E34" s="1" t="s">
+      <c r="E34" s="10" t="s">
         <v>212</v>
       </c>
-      <c r="F34" s="1" t="s">
+      <c r="F34" s="10" t="s">
         <v>212</v>
       </c>
-      <c r="G34" s="1" t="s">
+      <c r="G34" s="10" t="s">
         <v>212</v>
       </c>
-      <c r="H34" s="1" t="s">
+      <c r="H34" s="10" t="s">
         <v>212</v>
       </c>
-      <c r="I34" s="1" t="s">
+      <c r="I34" s="10" t="s">
         <v>212</v>
       </c>
-      <c r="J34" s="1" t="s">
+      <c r="J34" s="10" t="s">
         <v>212</v>
       </c>
-      <c r="K34" s="1" t="s">
+      <c r="K34" s="10" t="s">
         <v>212</v>
       </c>
     </row>
-    <row r="35">
-      <c r="A35" s="8" t="s">
+    <row r="35" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A35" s="7" t="s">
         <v>213</v>
       </c>
       <c r="B35" s="4"/>
@@ -2109,37 +2152,37 @@
       <c r="J35" s="4"/>
       <c r="K35" s="4"/>
     </row>
-    <row r="36">
-      <c r="A36" s="7"/>
-    </row>
-    <row r="37">
-      <c r="A37" s="7"/>
-    </row>
-    <row r="38">
-      <c r="A38" s="7"/>
-    </row>
-    <row r="39">
-      <c r="A39" s="7"/>
-    </row>
-    <row r="40">
-      <c r="A40" s="7"/>
-    </row>
-    <row r="41">
-      <c r="A41" s="7"/>
+    <row r="36" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A36" s="6"/>
+    </row>
+    <row r="37" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A37" s="6"/>
+    </row>
+    <row r="38" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A38" s="6"/>
+    </row>
+    <row r="39" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A39" s="6"/>
+    </row>
+    <row r="40" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A40" s="6"/>
+    </row>
+    <row r="41" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A41" s="6"/>
     </row>
   </sheetData>
   <mergeCells count="9">
+    <mergeCell ref="A16:K16"/>
+    <mergeCell ref="A24:K24"/>
+    <mergeCell ref="A32:K32"/>
+    <mergeCell ref="A34:K34"/>
     <mergeCell ref="B1:E1"/>
     <mergeCell ref="F1:G1"/>
     <mergeCell ref="H1:I1"/>
     <mergeCell ref="J1:K1"/>
     <mergeCell ref="A5:K5"/>
-    <mergeCell ref="A16:K16"/>
-    <mergeCell ref="A24:K24"/>
-    <mergeCell ref="A32:K32"/>
-    <mergeCell ref="A34:K34"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>
 </file>
--- a/Output/AllModels_SensitivityNoPushing_12000.xlsx
+++ b/Output/AllModels_SensitivityNoPushing_12000.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="188" uniqueCount="188">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="218" uniqueCount="218">
   <si>
     <t xml:space="preserve"/>
   </si>
@@ -506,24 +506,6 @@
     <t xml:space="preserve">[0.06, 1.53]</t>
   </si>
   <si>
-    <t xml:space="preserve">L3:sd(Daily individual's experienced persuasion)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">L3:sd(Daily partner's experienced persuasion)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">L3:sd(Daily individual's experienced pressure)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">L3:sd(Daily partner's experienced pressure)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">L3:sd(Daily individual's experienced pushing)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">L3:sd(Daily partner's experienced pushing)</t>
-  </si>
-  <si>
     <t xml:space="preserve">Random Effects (Level 2 - Couple:Person)</t>
   </si>
   <si>
@@ -555,6 +537,114 @@
   </si>
   <si>
     <t xml:space="preserve">[0.39, 2.00]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">L2:sd(Daily individual's experienced persuasion)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.35</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[0.15, 0.56]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.13</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[0.09, 0.17]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.06</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[0.03, 0.09]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[0.05, 0.15]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.31</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[0.02, 0.65]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">L2:sd(Daily partner's experienced persuasion)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[0.16, 0.56]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.07</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[0.02, 0.12]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[0.03, 0.10]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.08</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[0.03, 0.14]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.50</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[0.12, 0.98]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">L2:sd(Daily individual's experienced pressure)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.44</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[0.02, 1.43]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[0.00, 0.23]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.04</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[0.00, 0.13]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[0.00, 0.22]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.25</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[0.22, 2.89]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">L2:sd(Daily partner's experienced pressure)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.54</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[0.03, 1.78]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[0.00, 0.19]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[0.04, 3.19]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">L2:sd(Daily individual's experienced pushing)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">L2:sd(Daily partner's experienced pushing)</t>
   </si>
   <si>
     <t xml:space="preserve">Additional Parameters</t>
@@ -639,7 +729,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -657,6 +747,9 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment indent="1"/>
@@ -1715,223 +1808,303 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="7" t="s">
+      <c r="A26" s="8" t="s">
         <v>164</v>
       </c>
-      <c r="B26" s="1"/>
-      <c r="C26" s="1"/>
-      <c r="D26" s="1"/>
-      <c r="E26" s="1"/>
-      <c r="F26" s="1"/>
-      <c r="G26" s="1"/>
-      <c r="H26" s="1"/>
-      <c r="I26" s="1"/>
-      <c r="J26" s="1"/>
-      <c r="K26" s="1"/>
+      <c r="B26" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="C26" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="D26" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="E26" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="F26" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="G26" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="H26" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="I26" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="J26" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="K26" s="1" t="s">
+        <v>164</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="7" t="s">
         <v>165</v>
       </c>
-      <c r="B27" s="1"/>
-      <c r="C27" s="1"/>
-      <c r="D27" s="1"/>
-      <c r="E27" s="1"/>
-      <c r="F27" s="1"/>
-      <c r="G27" s="1"/>
-      <c r="H27" s="1"/>
-      <c r="I27" s="1"/>
-      <c r="J27" s="1"/>
-      <c r="K27" s="1"/>
+      <c r="B27" s="1" t="s">
+        <v>166</v>
+      </c>
+      <c r="C27" s="1" t="s">
+        <v>167</v>
+      </c>
+      <c r="D27" s="1" t="s">
+        <v>168</v>
+      </c>
+      <c r="E27" s="1" t="s">
+        <v>169</v>
+      </c>
+      <c r="F27" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="G27" s="1" t="s">
+        <v>170</v>
+      </c>
+      <c r="H27" s="1" t="s">
+        <v>171</v>
+      </c>
+      <c r="I27" s="1" t="s">
+        <v>172</v>
+      </c>
+      <c r="J27" s="1" t="s">
+        <v>173</v>
+      </c>
+      <c r="K27" s="1" t="s">
+        <v>174</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="7" t="s">
-        <v>166</v>
-      </c>
-      <c r="B28" s="1"/>
-      <c r="C28" s="1"/>
-      <c r="D28" s="1"/>
-      <c r="E28" s="1"/>
-      <c r="F28" s="1"/>
-      <c r="G28" s="1"/>
-      <c r="H28" s="1"/>
-      <c r="I28" s="1"/>
-      <c r="J28" s="1"/>
-      <c r="K28" s="1"/>
+        <v>175</v>
+      </c>
+      <c r="B28" s="1" t="s">
+        <v>176</v>
+      </c>
+      <c r="C28" s="1" t="s">
+        <v>177</v>
+      </c>
+      <c r="D28" s="1" t="s">
+        <v>178</v>
+      </c>
+      <c r="E28" s="1" t="s">
+        <v>179</v>
+      </c>
+      <c r="F28" s="1" t="s">
+        <v>180</v>
+      </c>
+      <c r="G28" s="1" t="s">
+        <v>181</v>
+      </c>
+      <c r="H28" s="1" t="s">
+        <v>182</v>
+      </c>
+      <c r="I28" s="1" t="s">
+        <v>183</v>
+      </c>
+      <c r="J28" s="1" t="s">
+        <v>184</v>
+      </c>
+      <c r="K28" s="1" t="s">
+        <v>185</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="7" t="s">
-        <v>167</v>
-      </c>
-      <c r="B29" s="1"/>
-      <c r="C29" s="1"/>
-      <c r="D29" s="1"/>
-      <c r="E29" s="1"/>
-      <c r="F29" s="1"/>
-      <c r="G29" s="1"/>
-      <c r="H29" s="1"/>
-      <c r="I29" s="1"/>
-      <c r="J29" s="1"/>
-      <c r="K29" s="1"/>
+        <v>186</v>
+      </c>
+      <c r="B29" s="1" t="s">
+        <v>176</v>
+      </c>
+      <c r="C29" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="D29" s="1" t="s">
+        <v>188</v>
+      </c>
+      <c r="E29" s="1" t="s">
+        <v>189</v>
+      </c>
+      <c r="F29" s="1" t="s">
+        <v>180</v>
+      </c>
+      <c r="G29" s="1" t="s">
+        <v>190</v>
+      </c>
+      <c r="H29" s="1" t="s">
+        <v>191</v>
+      </c>
+      <c r="I29" s="1" t="s">
+        <v>192</v>
+      </c>
+      <c r="J29" s="1" t="s">
+        <v>193</v>
+      </c>
+      <c r="K29" s="1" t="s">
+        <v>194</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="7" t="s">
-        <v>168</v>
-      </c>
-      <c r="B30" s="1"/>
-      <c r="C30" s="1"/>
-      <c r="D30" s="1"/>
-      <c r="E30" s="1"/>
-      <c r="F30" s="1"/>
-      <c r="G30" s="1"/>
-      <c r="H30" s="1"/>
-      <c r="I30" s="1"/>
-      <c r="J30" s="1"/>
-      <c r="K30" s="1"/>
+        <v>195</v>
+      </c>
+      <c r="B30" s="1" t="s">
+        <v>196</v>
+      </c>
+      <c r="C30" s="1" t="s">
+        <v>197</v>
+      </c>
+      <c r="D30" s="1" t="s">
+        <v>191</v>
+      </c>
+      <c r="E30" s="1" t="s">
+        <v>198</v>
+      </c>
+      <c r="F30" s="1" t="s">
+        <v>199</v>
+      </c>
+      <c r="G30" s="1" t="s">
+        <v>200</v>
+      </c>
+      <c r="H30" s="1" t="s">
+        <v>180</v>
+      </c>
+      <c r="I30" s="1" t="s">
+        <v>201</v>
+      </c>
+      <c r="J30" s="1" t="s">
+        <v>202</v>
+      </c>
+      <c r="K30" s="1" t="s">
+        <v>203</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="7" t="s">
-        <v>169</v>
-      </c>
-      <c r="B31" s="1"/>
-      <c r="C31" s="1"/>
-      <c r="D31" s="1"/>
-      <c r="E31" s="1"/>
-      <c r="F31" s="1"/>
-      <c r="G31" s="1"/>
-      <c r="H31" s="1"/>
-      <c r="I31" s="1"/>
-      <c r="J31" s="1"/>
-      <c r="K31" s="1"/>
+        <v>204</v>
+      </c>
+      <c r="B31" s="1" t="s">
+        <v>205</v>
+      </c>
+      <c r="C31" s="1" t="s">
+        <v>206</v>
+      </c>
+      <c r="D31" s="1" t="s">
+        <v>188</v>
+      </c>
+      <c r="E31" s="1" t="s">
+        <v>207</v>
+      </c>
+      <c r="F31" s="1" t="s">
+        <v>199</v>
+      </c>
+      <c r="G31" s="1" t="s">
+        <v>200</v>
+      </c>
+      <c r="H31" s="1" t="s">
+        <v>188</v>
+      </c>
+      <c r="I31" s="1" t="s">
+        <v>201</v>
+      </c>
+      <c r="J31" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="K31" s="1" t="s">
+        <v>208</v>
+      </c>
     </row>
     <row r="32">
-      <c r="A32" s="6" t="s">
-        <v>170</v>
-      </c>
-      <c r="B32" s="1" t="s">
-        <v>170</v>
-      </c>
-      <c r="C32" s="1" t="s">
-        <v>170</v>
-      </c>
-      <c r="D32" s="1" t="s">
-        <v>170</v>
-      </c>
-      <c r="E32" s="1" t="s">
-        <v>170</v>
-      </c>
-      <c r="F32" s="1" t="s">
-        <v>170</v>
-      </c>
-      <c r="G32" s="1" t="s">
-        <v>170</v>
-      </c>
-      <c r="H32" s="1" t="s">
-        <v>170</v>
-      </c>
-      <c r="I32" s="1" t="s">
-        <v>170</v>
-      </c>
-      <c r="J32" s="1" t="s">
-        <v>170</v>
-      </c>
-      <c r="K32" s="1" t="s">
-        <v>170</v>
-      </c>
+      <c r="A32" s="7" t="s">
+        <v>209</v>
+      </c>
+      <c r="B32" s="1"/>
+      <c r="C32" s="1"/>
+      <c r="D32" s="1"/>
+      <c r="E32" s="1"/>
+      <c r="F32" s="1"/>
+      <c r="G32" s="1"/>
+      <c r="H32" s="1"/>
+      <c r="I32" s="1"/>
+      <c r="J32" s="1"/>
+      <c r="K32" s="1"/>
     </row>
     <row r="33">
       <c r="A33" s="7" t="s">
-        <v>171</v>
-      </c>
-      <c r="B33" s="1" t="s">
-        <v>172</v>
-      </c>
-      <c r="C33" s="1" t="s">
-        <v>173</v>
-      </c>
-      <c r="D33" s="1" t="s">
-        <v>174</v>
-      </c>
-      <c r="E33" s="1" t="s">
-        <v>175</v>
-      </c>
-      <c r="F33" s="1" t="s">
-        <v>114</v>
-      </c>
-      <c r="G33" s="1" t="s">
-        <v>176</v>
-      </c>
-      <c r="H33" s="1" t="s">
-        <v>177</v>
-      </c>
-      <c r="I33" s="1" t="s">
-        <v>178</v>
-      </c>
-      <c r="J33" s="1" t="s">
-        <v>179</v>
-      </c>
-      <c r="K33" s="1" t="s">
-        <v>180</v>
-      </c>
+        <v>210</v>
+      </c>
+      <c r="B33" s="1"/>
+      <c r="C33" s="1"/>
+      <c r="D33" s="1"/>
+      <c r="E33" s="1"/>
+      <c r="F33" s="1"/>
+      <c r="G33" s="1"/>
+      <c r="H33" s="1"/>
+      <c r="I33" s="1"/>
+      <c r="J33" s="1"/>
+      <c r="K33" s="1"/>
     </row>
     <row r="34">
       <c r="A34" s="6" t="s">
-        <v>181</v>
+        <v>211</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>181</v>
+        <v>211</v>
       </c>
       <c r="C34" s="1" t="s">
-        <v>181</v>
+        <v>211</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>181</v>
+        <v>211</v>
       </c>
       <c r="E34" s="1" t="s">
-        <v>181</v>
+        <v>211</v>
       </c>
       <c r="F34" s="1" t="s">
-        <v>181</v>
+        <v>211</v>
       </c>
       <c r="G34" s="1" t="s">
-        <v>181</v>
+        <v>211</v>
       </c>
       <c r="H34" s="1" t="s">
-        <v>181</v>
+        <v>211</v>
       </c>
       <c r="I34" s="1" t="s">
-        <v>181</v>
+        <v>211</v>
       </c>
       <c r="J34" s="1" t="s">
-        <v>181</v>
+        <v>211</v>
       </c>
       <c r="K34" s="1" t="s">
-        <v>181</v>
+        <v>211</v>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="8" t="s">
-        <v>182</v>
+      <c r="A35" s="9" t="s">
+        <v>212</v>
       </c>
       <c r="B35" s="4"/>
       <c r="C35" s="4"/>
       <c r="D35" s="4" t="s">
-        <v>183</v>
+        <v>213</v>
       </c>
       <c r="E35" s="4" t="s">
-        <v>184</v>
+        <v>214</v>
       </c>
       <c r="F35" s="4" t="s">
-        <v>185</v>
+        <v>215</v>
       </c>
       <c r="G35" s="4" t="s">
-        <v>186</v>
+        <v>216</v>
       </c>
       <c r="H35" s="4" t="s">
         <v>141</v>
       </c>
       <c r="I35" s="4" t="s">
-        <v>187</v>
+        <v>217</v>
       </c>
       <c r="J35" s="4"/>
       <c r="K35" s="4"/>
@@ -1963,7 +2136,7 @@
     <mergeCell ref="A5:K5"/>
     <mergeCell ref="A16:K16"/>
     <mergeCell ref="A24:K24"/>
-    <mergeCell ref="A32:K32"/>
+    <mergeCell ref="A26:K26"/>
     <mergeCell ref="A34:K34"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
